--- a/Luban/Excel/场景.xlsx
+++ b/Luban/Excel/场景.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,8 +75,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-x|x|x|x（地区id|x坐标|y坐标|朝向）
-1左2右</t>
+x|x（x坐标|y坐标）
+</t>
         </r>
       </text>
     </comment>
@@ -194,7 +194,7 @@
     <t>默认场景交互</t>
   </si>
   <si>
-    <t>所在区域</t>
+    <t>小地图位置</t>
   </si>
   <si>
     <t>主角生成坐标</t>
@@ -212,10 +212,10 @@
     <t>默认开关</t>
   </si>
   <si>
-    <t>地图类型</t>
-  </si>
-  <si>
-    <t>前置地图</t>
+    <t>场景类型</t>
+  </si>
+  <si>
+    <t>场景地图</t>
   </si>
   <si>
     <t>背景美术资源</t>
